--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Scuola dell'infanzia.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Scuola dell'infanzia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="156">
   <si>
     <r>
       <t xml:space="preserve">
@@ -91,7 +91,7 @@
     <t>Domanda non accolta</t>
   </si>
   <si>
-    <t xml:space="preserve">Pubblicazioni graduatorie </t>
+    <t>Pubblicazioni graduatorie</t>
   </si>
   <si>
     <t>Domanda completata</t>
@@ -193,7 +193,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Vedi iscrizioni aperte</t>
+    <t>Consulta iscrizioni aperte</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -710,7 +710,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">  per l’anno educativo </t>
+      <t xml:space="preserve"> per l’anno educativo </t>
     </r>
     <r>
       <rPr>
@@ -727,7 +727,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -988,7 +988,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Sarà possibile consultare la propria posizione in graduatoria dal </t>
     </r>
     <r>
@@ -1119,7 +1119,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> non è stata accolta. 
+      <t xml:space="preserve"> non è stata accolta.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -1181,7 +1181,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> per  l’anno educativo </t>
+      <t xml:space="preserve"> per l’anno educativo </t>
     </r>
     <r>
       <rPr>
@@ -1295,7 +1295,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> per l'anno educativo  </t>
+      <t xml:space="preserve"> per l'anno educativo </t>
     </r>
     <r>
       <rPr>
@@ -1329,7 +1329,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> . 
+      <t xml:space="preserve"> .
 </t>
     </r>
     <r>
@@ -1569,7 +1569,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">. - 
+
 </t>
     </r>
     <r>
@@ -1604,7 +1604,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> € 
+      <t xml:space="preserve"> €
 </t>
     </r>
     <r>
@@ -1640,8 +1640,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve"> - 
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Se hai già provveduto a pagare l'avviso ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.</t>
     </r>
@@ -1649,20 +1649,11 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <family val="2"/>
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>I nuovi iscritti o già iscritti possono comunicare l'interesse a richiedere una retta agevolata o ridotta se:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> 
+      <t xml:space="preserve">I nuovi iscritti o già iscritti possono comunicare l'interesse a richiedere una retta agevolata o ridotta se:
 </t>
     </r>
     <r>
@@ -1680,7 +1671,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> 
+      <t xml:space="preserve">
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -2047,7 +2038,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">.
-Ricarica il tuo borsellino elettronico con l'importo dovuto entro la data di scadenza. 
+Ricarica il tuo borsellino elettronico con l'importo dovuto entro la data di scadenza.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -2093,7 +2084,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">.
-Ricarica ora per saldare l'importo dovuto. Per farlo, [sito](URL). 
+Ricarica ora per saldare l'importo dovuto. Per farlo, [sito](URL).
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -2117,19 +2108,19 @@
     <t>Vai alla tua domanda</t>
   </si>
   <si>
+    <t>Aggiungi documenti</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
     <t>Vai alla graduatoria</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
-    <t>Scopri tutte le agevolazioni</t>
-  </si>
-  <si>
-    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
+    <t>Scopri le agevolazioni disponibili</t>
   </si>
   <si>
     <r>
@@ -2149,7 +2140,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -2265,14 +2256,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -3139,46 +3122,46 @@
         <v>120</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G6" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="H6" s="34" t="s">
-        <v>120</v>
-      </c>
       <c r="I6" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J6" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K6" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L6" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="M6" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="M6" s="34" t="s">
-        <v>124</v>
-      </c>
       <c r="N6" s="34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O6" s="34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q6" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R6" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3242,55 +3225,55 @@
         <v>126</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R8" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3443,13 +3426,13 @@
         <v>67</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P11" s="34" t="s">
         <v>67</v>
